--- a/docs/downloads/05/tbl_comfort_alaotra_ambodivoara.xlsx
+++ b/docs/downloads/05/tbl_comfort_alaotra_ambodivoara.xlsx
@@ -383,10 +383,10 @@
         </is>
       </c>
       <c r="C2">
-        <v>171</v>
+        <v>361</v>
       </c>
       <c r="D2">
-        <v>100</v>
+        <v>622.4</v>
       </c>
     </row>
     <row r="3">
@@ -396,10 +396,10 @@
         </is>
       </c>
       <c r="C3">
-        <v>1428</v>
+        <v>3056</v>
       </c>
       <c r="D3">
-        <v>100</v>
+        <v>602.8</v>
       </c>
     </row>
   </sheetData>
